--- a/30-Ket-Qua/2026-10-21/Tham-dinh/PL-V_Bang-tinh-hieu-qua-Hang-A_20261021_sua-cong-thuc.xlsx
+++ b/30-Ket-Qua/2026-10-21/Tham-dinh/PL-V_Bang-tinh-hieu-qua-Hang-A_20261021_sua-cong-thuc.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thảo 2026\Khoa Đào tạo lái xe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.CLAUDE code\KTC-Quan-tri\30-Ket-Qua\2026-10-21\Tham-dinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD60B18-8850-4149-AF82-C97A97138000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="11505" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="2928" yWindow="2172" windowWidth="10428" windowHeight="10068" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="lộ trình hp" sheetId="2" r:id="rId1"/>
-    <sheet name="Nội dung khoán THU CHI thuê sân" sheetId="5" r:id="rId2"/>
-    <sheet name="Nội dung khoán tHU CHI học phí" sheetId="4" r:id="rId3"/>
-    <sheet name="Dự toán thu - chi" sheetId="11" r:id="rId4"/>
-    <sheet name="Khấu hao" sheetId="7" r:id="rId5"/>
+    <sheet name="lộ trình hp" sheetId="1" r:id="rId1"/>
+    <sheet name="Nội dung khoán THU CHI thuê sân" sheetId="2" r:id="rId2"/>
+    <sheet name="Nội dung khoán tHU CHI học phí" sheetId="3" r:id="rId3"/>
+    <sheet name="Dự toán thu - chi" sheetId="4" r:id="rId4"/>
+    <sheet name="Khấu hao" sheetId="5" r:id="rId5"/>
     <sheet name="Dự kiến thu" sheetId="6" r:id="rId6"/>
+    <sheet name="Độ nhạy" sheetId="7" r:id="rId7"/>
+    <sheet name="Ghi chú rà soát" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -40,13 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="136">
-  <si>
-    <t>Doanh thu</t>
-  </si>
-  <si>
-    <t>Chỉ tiêu</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="180">
   <si>
     <t>STT</t>
   </si>
@@ -76,6 +70,9 @@
   </si>
   <si>
     <t>Phụ lục I</t>
+  </si>
+  <si>
+    <t>PHÂN KHAI LỆ PHÍ SÁT HẠCH LÁI XE MÔ TÔ HẠNG A</t>
   </si>
   <si>
     <t>TT</t>
@@ -94,380 +91,503 @@
     <t>A</t>
   </si>
   <si>
+    <t>Doanh thu</t>
+  </si>
+  <si>
+    <t>Cho thuê sân ôn luyện sát hạch</t>
+  </si>
+  <si>
+    <t>Số lượt</t>
+  </si>
+  <si>
+    <t>Lượt</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
+  </si>
+  <si>
+    <t>Đồng</t>
+  </si>
+  <si>
+    <t>Thuê sân phục vụ sát hạch (53% lp)</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chi phí </t>
+  </si>
+  <si>
+    <t>Nhiên liệu</t>
+  </si>
+  <si>
+    <t>Chi phí nhiên liệu phục vụ cho thuê ôn luyện</t>
+  </si>
+  <si>
+    <t>Chi phí nhiên liệu phục vụ sát hạch A</t>
+  </si>
+  <si>
+    <t>Khấu hao phần lý thuyết sát hạch lái xe</t>
+  </si>
+  <si>
     <t>Học viên</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chi phí </t>
-  </si>
-  <si>
-    <t>Nhiên liệu</t>
+    <t>Khấu hao phần sát hạch thực hành</t>
+  </si>
+  <si>
+    <t>Bảo dưỡng, sửa chữa nhỏ thiết bị</t>
+  </si>
+  <si>
+    <t>Bảo dưỡng, sửa chữa nhỏ sân bãi</t>
+  </si>
+  <si>
+    <t>Văn phòng phẩm phục vụ sát hạch A</t>
+  </si>
+  <si>
+    <t>Khoán kinh phí vệ sinh phục vụ sát hạch A</t>
+  </si>
+  <si>
+    <t>Chi phí lương bộ phận trực tiếp cho thuê sân</t>
+  </si>
+  <si>
+    <t>Chi phí lương bộ phận quản lý chung</t>
+  </si>
+  <si>
+    <t>Chi phí quản lý chung đào tạo, sát hạch mô tô</t>
+  </si>
+  <si>
+    <t>Thuế TNDN, GTGT thuê sân sát hạch</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Chênh lệch thu - Chi</t>
+  </si>
+  <si>
+    <t>Quảng Ngãi, ngày    tháng   năm 2026</t>
+  </si>
+  <si>
+    <t>KHOA ĐT&amp;SHLX</t>
+  </si>
+  <si>
+    <t>PHÒNG TC-KT</t>
+  </si>
+  <si>
+    <t>HIỆU TRƯỞNG</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Thành</t>
+  </si>
+  <si>
+    <t>Huỳnh Thị Tuyết</t>
+  </si>
+  <si>
+    <t>Lê Trí Khải</t>
+  </si>
+  <si>
+    <t>PHÂN KHAI HỌC PHÍ ĐÀO TẠO LÁI XE MÔ TÔ HẠNG A</t>
+  </si>
+  <si>
+    <t>Mức khoán</t>
+  </si>
+  <si>
+    <t>Năm thứ 1</t>
+  </si>
+  <si>
+    <t>Năm thứ 2</t>
+  </si>
+  <si>
+    <t>Năm thứ 3</t>
+  </si>
+  <si>
+    <t>Năm thứ 4</t>
+  </si>
+  <si>
+    <t>Năm thứ 5</t>
+  </si>
+  <si>
+    <t>Doanh thu (=1 x2)</t>
+  </si>
+  <si>
+    <t>Chi phí =(1+2+3+…+11+12)</t>
+  </si>
+  <si>
+    <t>Khoán nhiên liệu</t>
+  </si>
+  <si>
+    <t>Khấu hao cơ sở vật chất phần lý thuyết đào tạo lái xe</t>
   </si>
   <si>
     <t>Khấu hao phần đào tạo thực hành</t>
   </si>
   <si>
-    <t>Khấu hao phần lý thuyết sát hạch lái xe</t>
-  </si>
-  <si>
-    <t>Khấu hao phần sát hạch thực hành</t>
-  </si>
-  <si>
-    <t>Bảo dưỡng, sửa chữa nhỏ thiết bị</t>
-  </si>
-  <si>
-    <t>Bảo dưỡng, sửa chữa nhỏ sân bãi</t>
-  </si>
-  <si>
-    <t>Chi phí quản lý chung đào tạo, sát hạch mô tô</t>
+    <t>Tiền lương giảng dạy lý thuyết</t>
+  </si>
+  <si>
+    <t>Khoán lương dạy thực hành</t>
+  </si>
+  <si>
+    <t>Khoán thuê phương tiện</t>
+  </si>
+  <si>
+    <t>Khoán tuyển sinh</t>
+  </si>
+  <si>
+    <t>Khoán văn phòng phẩm phục vụ đào tạo A</t>
+  </si>
+  <si>
+    <t>Chi phí lương cho bộ phận quản lý (10% lương trực tiếp)</t>
+  </si>
+  <si>
+    <t>Đào tạo bồi dưỡng (2027:09GV)</t>
+  </si>
+  <si>
+    <t>61.2</t>
   </si>
   <si>
     <t xml:space="preserve">Thuế TNDN học phí </t>
   </si>
   <si>
-    <t>Thuế TNDN, GTGT thuê sân sát hạch</t>
-  </si>
-  <si>
-    <t>Chênh lệch thu - Chi</t>
-  </si>
-  <si>
-    <t>KHOA ĐT&amp;SHLX</t>
-  </si>
-  <si>
-    <t>PHÒNG TC-KT</t>
-  </si>
-  <si>
-    <t>HIỆU TRƯỞNG</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Thành</t>
-  </si>
-  <si>
-    <t>Huỳnh Thị Tuyết</t>
-  </si>
-  <si>
-    <t>Lê Trí Khải</t>
-  </si>
-  <si>
-    <t>Khoán nhiên liệu</t>
-  </si>
-  <si>
-    <t>Khoán văn phòng phẩm phục vụ đào tạo A</t>
-  </si>
-  <si>
-    <t>Khoán tuyển sinh</t>
-  </si>
-  <si>
-    <t>Khoán thuê phương tiện</t>
-  </si>
-  <si>
-    <t>Khoán lương dạy thực hành</t>
-  </si>
-  <si>
-    <t>Tiền lương giảng dạy lý thuyết</t>
-  </si>
-  <si>
-    <t>Khấu hao cơ sở vật chất phần lý thuyết đào tạo lái xe</t>
-  </si>
-  <si>
-    <t>Quảng Ngãi, ngày    tháng   năm 2026</t>
-  </si>
-  <si>
-    <t>PHÂN KHAI LỆ PHÍ SÁT HẠCH LÁI XE MÔ TÔ HẠNG A</t>
-  </si>
-  <si>
-    <t>Cho thuê sân ôn luyện sát hạch</t>
-  </si>
-  <si>
-    <t>Lượt</t>
-  </si>
-  <si>
-    <t>Thuê sân phục vụ sát hạch (53% lp)</t>
-  </si>
-  <si>
-    <t>Chi phí nhiên liệu phục vụ cho thuê ôn luyện</t>
-  </si>
-  <si>
-    <t>Văn phòng phẩm phục vụ sát hạch A</t>
-  </si>
-  <si>
-    <t>Chi phí nhiên liệu phục vụ sát hạch A</t>
-  </si>
-  <si>
-    <t>Số học viên đào tạo (dự kiến bình quân 45 HV/khoá)</t>
-  </si>
-  <si>
-    <t>Học phí/học viên (dự kiến)</t>
-  </si>
-  <si>
-    <t>Tổng doanh thu dự kiến/năm</t>
-  </si>
-  <si>
-    <t>Tổng doanh thu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đơn giá cho thuê </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số lượt cho thuê thiết bị ôn luyện </t>
-  </si>
-  <si>
-    <t>Số lượt cho thuê thiết bị sát hạch</t>
-  </si>
-  <si>
-    <t>Khoán kinh phí vệ sinh phục vụ sát hạch A</t>
-  </si>
-  <si>
-    <t>Mức khoán</t>
-  </si>
-  <si>
-    <t>Số lượng</t>
-  </si>
-  <si>
-    <t>Doanh thu (=1 x2)</t>
-  </si>
-  <si>
-    <t>Chi phí =(1+2+3+…+11+12)</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>PHÂN KHAI HỌC PHÍ ĐÀO TẠO LÁI XE MÔ TÔ HẠNG A</t>
-  </si>
-  <si>
-    <t>Số lượt</t>
-  </si>
-  <si>
-    <t>Đơn giá</t>
-  </si>
-  <si>
-    <t>Đồng</t>
+    <t>PHÂN KHAI HỌC PHÍ ĐÀO TẠO, SÁT HẠCH LÁI XE MÔ TÔ HẠNG A</t>
+  </si>
+  <si>
+    <t>ĐVT: Triệu đồng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doanh thu </t>
+  </si>
+  <si>
+    <t>Đào tạo lái xe mô tô hạng A</t>
+  </si>
+  <si>
+    <t>Cho thuê sân, thiết bị ôn luyện hạng A</t>
+  </si>
+  <si>
+    <t>Cho thuê sân, thiết bị sát hạch hạng A</t>
+  </si>
+  <si>
+    <t>Khấu hao cơ sở vật chất</t>
+  </si>
+  <si>
+    <t>Khoán lương bộ phận trực tiếp cho thuê xe và sân</t>
+  </si>
+  <si>
+    <t>Khoán văn phòng phẩm phục vụ đào tạo, sát hạch A</t>
+  </si>
+  <si>
+    <t>Chi phí lương cho bộ phận quản lý (15% lương TT)</t>
+  </si>
+  <si>
+    <t>Chi phí quản lý chung đào tạo, sát hạch mô tô (10%)</t>
+  </si>
+  <si>
+    <t>Chi phí hoạt động (điện, nước…)</t>
+  </si>
+  <si>
+    <t>Nộp thuế GTGT (ước tính)</t>
+  </si>
+  <si>
+    <t>Nộp thuế TNDN</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Lợi nhuận sau thuế</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Xác định thời gian hoàn vốn đầu tư</t>
+  </si>
+  <si>
+    <t>Tổng vốn đầu tư</t>
+  </si>
+  <si>
+    <t>Dòng tiền</t>
+  </si>
+  <si>
+    <t>Thời gian hoàn vốn</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Dòng tiền lũy kế</t>
   </si>
   <si>
     <t>PHỤ LỤC</t>
-  </si>
-  <si>
-    <t>ĐVT: Triệu đồng</t>
-  </si>
-  <si>
-    <t>Nội dung</t>
-  </si>
-  <si>
-    <t>Đơn vị tính</t>
-  </si>
-  <si>
-    <t>Nguyên giá</t>
-  </si>
-  <si>
-    <t>Tỷ lệ khấu hao</t>
-  </si>
-  <si>
-    <t>Mức khấu hao hàng năm</t>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <r>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>Thời gian sử dụng 10 năm</t>
-  </si>
-  <si>
-    <t>Hệ thống</t>
-  </si>
-  <si>
-    <t>Thời gian sử dụng 8 năm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng </t>
-  </si>
-  <si>
-    <t>Phòng học lý thuyết</t>
-  </si>
-  <si>
-    <t>Phòng máy vi tính</t>
-  </si>
-  <si>
-    <t>Thời gian sử dụng 20 năm</t>
-  </si>
-  <si>
-    <t>Bộ</t>
-  </si>
-  <si>
-    <t>Nhà điều hành số 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sân tập </t>
-  </si>
-  <si>
-    <t>Sân sát hạch bài tổng hợp số 1</t>
-  </si>
-  <si>
-    <t>Sân sát hạch bài tổng hợp số 2</t>
-  </si>
-  <si>
-    <t>Xe mô tô sát hạch Hạng A (Honda CB350 H'ness)</t>
-  </si>
-  <si>
-    <t>Thiết bị chấm điểm tự động trên xe sát hạch Hạng A, trên sân và tại phòng điều hành sát hạch thực hành Hạng A (module điều khiển chính, module hiển thị và camera, module tần số radio, phần mềm)</t>
-  </si>
-  <si>
-    <t>Thiết bị, phần mềm sát hạch xử lý tình huống giả định trên đường Hạng A1, A</t>
   </si>
   <si>
     <t>TÍNH KHẤU HAO CƠ SỞ VẬT CHẤT  VÀ TRANG THIẾT BỊ HỤC VỤ CHO 
 ĐÀO TẠO VÀ SÁT HẠCH HẠNG A</t>
   </si>
   <si>
+    <t>Nội dung</t>
+  </si>
+  <si>
+    <t>Đơn vị tính</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>Nguyên giá</t>
+  </si>
+  <si>
+    <t>Tần suất sử dụng</t>
+  </si>
+  <si>
+    <t>Nguyên giá sử dụng</t>
+  </si>
+  <si>
+    <t>Tỷ lệ khấu hao</t>
+  </si>
+  <si>
+    <t>Mức khấu hao hàng năm</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>7=5*6</t>
+  </si>
+  <si>
+    <t>9=7x8</t>
+  </si>
+  <si>
+    <t>Phòng học lý thuyết</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Thời gian sử dụng 20 năm</t>
+  </si>
+  <si>
+    <t>Phòng máy vi tính</t>
+  </si>
+  <si>
+    <t>Máy vi tính (30 máy trạm, 2 máy chủ)</t>
+  </si>
+  <si>
+    <t>Bộ</t>
+  </si>
+  <si>
+    <t>Thời gian sử dụng 7 năm</t>
+  </si>
+  <si>
+    <t>Nhà điều hành số 2</t>
+  </si>
+  <si>
+    <t>Nhà</t>
+  </si>
+  <si>
+    <t>Thời gian sử dụng 15 năm</t>
+  </si>
+  <si>
+    <t>Xe mô tô sát hạch Hạng A (Honda CB350 H'ness)</t>
+  </si>
+  <si>
+    <t>Chiếc</t>
+  </si>
+  <si>
+    <t>Thời gian sử dụng 10 năm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sân tập </t>
+  </si>
+  <si>
+    <t>sân</t>
+  </si>
+  <si>
+    <t>Sân sát hạch bài tổng hợp số 1</t>
+  </si>
+  <si>
     <t>Sân</t>
   </si>
   <si>
-    <t>Nhà</t>
-  </si>
-  <si>
-    <t>sân</t>
-  </si>
-  <si>
-    <t>Chiếc</t>
-  </si>
-  <si>
-    <t>Thời gian sử dụng 7 năm</t>
+    <t>Sân sát hạch bài tổng hợp số 2</t>
+  </si>
+  <si>
+    <t>Thiết bị chấm điểm tự động trên xe sát hạch Hạng A, trên sân và tại phòng điều hành sát hạch thực hành Hạng A (module điều khiển chính, module hiển thị và camera, module tần số radio, phần mềm)</t>
+  </si>
+  <si>
+    <t>Hệ thống</t>
   </si>
   <si>
     <t>Thời gian sử dụng 5 năm</t>
   </si>
   <si>
-    <t>Thời gian sử dụng 15 năm</t>
-  </si>
-  <si>
-    <t>Năm thứ 1</t>
-  </si>
-  <si>
-    <t>Năm thứ 2</t>
-  </si>
-  <si>
-    <t>Năm thứ 3</t>
-  </si>
-  <si>
-    <t>Năm thứ 4</t>
-  </si>
-  <si>
-    <t>Năm thứ 5</t>
-  </si>
-  <si>
-    <t>Nộp thuế GTGT (ước tính)</t>
-  </si>
-  <si>
-    <t>Nộp thuế TNDN</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Lợi nhuận sau thuế</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Xác định thời gian hoàn vốn đầu tư</t>
-  </si>
-  <si>
-    <t>Tổng vốn đầu tư</t>
-  </si>
-  <si>
-    <t>Dòng tiền</t>
-  </si>
-  <si>
-    <t>Thời gian hoàn vốn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doanh thu </t>
-  </si>
-  <si>
-    <t>Đào tạo lái xe mô tô hạng A</t>
-  </si>
-  <si>
-    <t>Cho thuê sân, thiết bị ôn luyện hạng A</t>
-  </si>
-  <si>
-    <t>Cho thuê sân, thiết bị sát hạch hạng A</t>
-  </si>
-  <si>
-    <t>Khấu hao cơ sở vật chất</t>
-  </si>
-  <si>
-    <t>Tần suất sử dụng</t>
-  </si>
-  <si>
-    <t>Khoán văn phòng phẩm phục vụ đào tạo, sát hạch A</t>
-  </si>
-  <si>
-    <t>Đào tạo bồi dưỡng (2027:09GV)</t>
-  </si>
-  <si>
-    <t>Chi phí hoạt động (điện, nước…)</t>
-  </si>
-  <si>
-    <t>PHÂN KHAI HỌC PHÍ ĐÀO TẠO, SÁT HẠCH LÁI XE MÔ TÔ HẠNG A</t>
+    <t>Thiết bị, phần mềm sát hạch xử lý tình huống giả định trên đường Hạng A1, A</t>
   </si>
   <si>
     <t>Thiết bị hỗ trợ sát hạch: Bộ đàm; hệ thống âm thanh; màn hình hiển thị; camera giám sát; máy phát điện dự phòng; thiết bị lưu điện</t>
   </si>
   <si>
-    <t>Máy vi tính (30 máy trạm, 2 máy chủ)</t>
-  </si>
-  <si>
-    <t>Chi phí lương cho bộ phận quản lý (10% lương trực tiếp)</t>
-  </si>
-  <si>
-    <t>Chi phí lương bộ phận trực tiếp cho thuê sân</t>
-  </si>
-  <si>
-    <t>Chi phí lương bộ phận quản lý chung</t>
-  </si>
-  <si>
-    <t>Khoán lương bộ phận trực tiếp cho thuê xe và sân</t>
-  </si>
-  <si>
-    <t>Chi phí lương cho bộ phận quản lý (15% lương TT)</t>
-  </si>
-  <si>
-    <t>Chi phí quản lý chung đào tạo, sát hạch mô tô (10%)</t>
-  </si>
-  <si>
-    <t>61.2</t>
-  </si>
-  <si>
-    <t>Nguyên giá sử dụng</t>
-  </si>
-  <si>
-    <t>7=5*6</t>
-  </si>
-  <si>
-    <t>9=7x8</t>
+    <t>Thời gian sử dụng 8 năm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổng </t>
+  </si>
+  <si>
+    <t>Chỉ tiêu</t>
+  </si>
+  <si>
+    <t>Số học viên đào tạo (dự kiến bình quân 45 HV/khoá)</t>
+  </si>
+  <si>
+    <t>Học phí/học viên (dự kiến)</t>
+  </si>
+  <si>
+    <t>Tổng doanh thu dự kiến/năm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số lượt cho thuê thiết bị ôn luyện </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đơn giá cho thuê </t>
+  </si>
+  <si>
+    <t>Tổng doanh thu</t>
+  </si>
+  <si>
+    <t>Số lượt cho thuê thiết bị sát hạch</t>
+  </si>
+  <si>
+    <t>PHÂN TÍCH ĐỘ NHẠY THEO SỐ HỌC VIÊN HẠNG A</t>
+  </si>
+  <si>
+    <t>Đơn vị tính: triệu đồng. Tính bằng cùng công thức sheet "Dự toán thu - chi" (giữ nguyên khấu hao, chi bồi dưỡng; các khoản khác theo tỷ lệ doanh thu). Bảng giá trị, do AI tính ngày 21/10/2026 — phòng TC-KT kiểm tra lại.</t>
+  </si>
+  <si>
+    <t>Kịch bản</t>
+  </si>
+  <si>
+    <t>Thời gian hoàn vốn (năm)</t>
+  </si>
+  <si>
+    <t>100% kế hoạch (Bảng 7)</t>
+  </si>
+  <si>
+    <t>Chi phí</t>
+  </si>
+  <si>
+    <t>70% kế hoạch</t>
+  </si>
+  <si>
+    <t>Chưa hoàn vốn trong 5 năm</t>
+  </si>
+  <si>
+    <t>50% kế hoạch</t>
+  </si>
+  <si>
+    <t>Vốn đầu tư dùng làm mẫu số: 1,505.18 triệu đồng ('Khấu hao'!G17). Nếu dùng vốn đầu tư mới tại Bảng 10 (1.730,2 triệu đồng), kịch bản 100% chưa hoàn vốn trong 5 năm.</t>
+  </si>
+  <si>
+    <t>Vị trí</t>
+  </si>
+  <si>
+    <t>Nội dung rà soát (21/10/2026)</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Dự toán thu - chi!C29</t>
+  </si>
+  <si>
+    <t>Công thức hoàn vốn cũ chia dòng tiền 5 năm cho 4, cho kết quả 3,83 năm. Đã thay bằng cách tính theo dòng tiền lũy kế (dòng 30): kết quả ≈ 4,86 năm.</t>
+  </si>
+  <si>
+    <t>Đã sửa</t>
+  </si>
+  <si>
+    <t>Nội dung khoán tHU CHI học phí!F15:I15</t>
+  </si>
+  <si>
+    <t>Năm 1 tính (lương LT + TH) × 10%, năm 2–5 tính 10% doanh thu: không thống nhất. Đã thống nhất theo năm 1. Dòng này không chuyển sang sheet tổng hợp.</t>
+  </si>
+  <si>
+    <t>Nội dung khoán THU CHI thuê sân!F23:I23</t>
+  </si>
+  <si>
+    <t>Năm 1 tính theo lương trực tiếp, năm 2–5 tính theo doanh thu cho thuê ôn luyện: không thống nhất. Đã thống nhất theo năm 1. Dòng 23 chưa được cộng vào tổng chi phí (dòng 12): đề nghị TC-KT xác định có tính hay không.</t>
+  </si>
+  <si>
+    <t>Đã sửa công thức; chờ TC-KT</t>
+  </si>
+  <si>
+    <t>Dự kiến thu!B14:C14</t>
+  </si>
+  <si>
+    <t>Lượt thuê sân sát hạch năm 2027 là 500, năm 2028 là 525: lớn hơn số học viên (220; 600), trong khi Trường chỉ sát hạch Hạng A sau khi được cấp lại giấy phép. Đề xuất 2027 = 0; từ 2028 = học viên × 1,2 như các năm sau.</t>
+  </si>
+  <si>
+    <t>Chờ TC-KT</t>
+  </si>
+  <si>
+    <t>lộ trình hp!D8:F8</t>
+  </si>
+  <si>
+    <t>Đơn giá thuê thiết bị ôn luyện tăng 10%/năm từ 2029; thân Đề án ghi tăng 5%/năm.</t>
+  </si>
+  <si>
+    <t>lộ trình hp!A7</t>
+  </si>
+  <si>
+    <t>"Mức thu cho thuê xe tập luyện 300.000 đ/giờ" không được dùng trong doanh thu. Bỏ dòng hoặc bổ sung doanh thu tương ứng.</t>
+  </si>
+  <si>
+    <t>Nội dung khoán THU CHI thuê sân!A2, E11</t>
+  </si>
+  <si>
+    <t>Tiêu đề "LỆ PHÍ sát hạch" nên là phí sát hạch (TT 154/2025/TT-BTC) hoặc giá dịch vụ sử dụng sân, thiết bị. Mức 53% × 130.000 đ cần ghi căn cứ (thỏa thuận với Phòng CSGT hoặc thực tế thu Hạng A1 năm 2025).</t>
+  </si>
+  <si>
+    <t>Khấu hao!G17; Dự toán thu - chi!C27</t>
+  </si>
+  <si>
+    <t>Tổng vốn đầu tư 1.505,18 triệu gồm cả tài sản đã có (phòng học, phòng máy, 03 sân tập A1). Đề xuất: hoàn vốn tính trên vốn đầu tư mới; khấu hao tài sản cũ chỉ đưa vào chi phí.</t>
+  </si>
+  <si>
+    <t>Khấu hao!E13, E14, F15</t>
+  </si>
+  <si>
+    <t>Sân bài số 2: 590 triệu đã là phần phân bổ theo diện tích (900/2.000 m² của 1.310,2 triệu) nhưng còn nhân 50%. Thiết bị chấm điểm 150 triệu khác báo giá EcoTek 198,7 triệu và Bảng 10 (200 triệu). Tỷ lệ 30% bài số 2 nên theo số lượt sát hạch A/A1 (khoảng 10–12%).</t>
+  </si>
+  <si>
+    <t>Dự toán thu - chi!C23:G24</t>
+  </si>
+  <si>
+    <t>Thuế TNDN đang tính theo tỷ lệ % trên doanh thu (2%, 5%), trong khi bảng đã hạch toán chi phí; đối chiếu NĐ 320/2025/NĐ-CP. Học phí A1 theo QĐ 572/QĐ-CĐKT ghi đã gồm GTGT 5% — thống nhất cách tính cho Hạng A.</t>
+  </si>
+  <si>
+    <t>Nội dung khoán tHU CHI học phí!D7:D14</t>
+  </si>
+  <si>
+    <t>Tổng tỷ lệ khoán trực tiếp trên học phí 67% (cao hơn mức 55–60% đã khảo sát tại Gia Lai).</t>
+  </si>
+  <si>
+    <t>Chờ Lãnh đạo</t>
+  </si>
+  <si>
+    <t>Các sheet</t>
+  </si>
+  <si>
+    <t>Tiêu đề các sheet ghi "Phụ lục I" và có phần ký: bảng tính kèm Đề án là Phụ lục V, đề nghị bỏ phần ký hoặc thống nhất số phụ lục.</t>
+  </si>
+  <si>
+    <t>Chờ Tổ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -475,7 +595,7 @@
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,13 +707,6 @@
       <family val="1"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,6 +733,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -629,7 +765,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -724,13 +860,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -771,7 +946,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -803,7 +978,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -876,9 +1051,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -892,10 +1067,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -904,7 +1079,7 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -930,7 +1105,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -939,7 +1114,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -964,19 +1139,19 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -986,7 +1161,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -996,30 +1171,61 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1027,32 +1233,35 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1071,171 +1280,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2523196</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>24765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>26856</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="2" name="Straight Connector 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{444C0E15-FFD7-4D90-B583-1144CBF26D44}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2799421" y="501015"/>
-          <a:ext cx="2467904" cy="2091"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2523196</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>24765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>26856</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="2" name="Straight Connector 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{444C0E15-FFD7-4D90-B583-1144CBF26D44}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2799421" y="501015"/>
-          <a:ext cx="2467904" cy="2091"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>135596</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>26856</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>26856</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="2" name="Straight Connector 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{444C0E15-FFD7-4D90-B583-1144CBF26D44}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3189946" y="471356"/>
-          <a:ext cx="2867954" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1534,47 +1578,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A5:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="6" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="6" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="D5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="E5" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="F5" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="31" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="32" t="s">
         <v>6</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>8</v>
       </c>
       <c r="B6" s="81">
         <v>2.35</v>
       </c>
       <c r="C6" s="81">
-        <f>B6*(1+5%)</f>
+        <f t="shared" ref="C6:F7" si="0">B6*(1+5%)</f>
         <v>2.4675000000000002</v>
       </c>
       <c r="D6" s="81">
-        <f t="shared" ref="D6:F6" si="0">C6*(1+5%)</f>
+        <f t="shared" si="0"/>
         <v>2.5908750000000005</v>
       </c>
       <c r="E6" s="81">
@@ -1586,131 +1630,131 @@
         <v>2.8564396875000009</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="82">
         <v>0.3</v>
       </c>
       <c r="C7" s="82">
-        <f t="shared" ref="C7:F8" si="1">B7*(1+5%)</f>
+        <f t="shared" si="0"/>
         <v>0.315</v>
       </c>
       <c r="D7" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.33075000000000004</v>
       </c>
       <c r="E7" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.34728750000000008</v>
       </c>
       <c r="F7" s="82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.36465187500000013</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="82">
         <v>0.05</v>
       </c>
       <c r="C8" s="82">
-        <f t="shared" si="1"/>
+        <f>B8*(1+5%)</f>
         <v>5.2500000000000005E-2</v>
       </c>
       <c r="D8" s="82">
-        <f t="shared" ref="D8:F8" si="2">C8*(1+10%)</f>
+        <f>C8*(1+10%)</f>
         <v>5.775000000000001E-2</v>
       </c>
       <c r="E8" s="82">
-        <f t="shared" si="2"/>
+        <f>D8*(1+10%)</f>
         <v>6.3525000000000012E-2</v>
       </c>
       <c r="F8" s="82">
-        <f t="shared" si="2"/>
+        <f>E8*(1+10%)</f>
         <v>6.9877500000000023E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="25" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+    </row>
+    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+    </row>
+    <row r="4" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-    </row>
-    <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -1719,28 +1763,28 @@
         <v>45.45</v>
       </c>
       <c r="F5" s="86">
-        <f t="shared" ref="F5:I5" si="0">F6+F9</f>
+        <f>F6+F9</f>
         <v>67.672499999999999</v>
       </c>
       <c r="G5" s="86">
-        <f t="shared" si="0"/>
+        <f>G6+G9</f>
         <v>96.89670000000001</v>
       </c>
       <c r="H5" s="86">
-        <f t="shared" si="0"/>
+        <f>H6+H9</f>
         <v>116.96400000000001</v>
       </c>
       <c r="I5" s="86">
-        <f t="shared" si="0"/>
+        <f>I6+I9</f>
         <v>140.35290000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D6" s="29"/>
       <c r="E6" s="83">
@@ -1748,29 +1792,29 @@
         <v>11</v>
       </c>
       <c r="F6" s="83">
-        <f t="shared" ref="F6:I6" si="1">F7*F8</f>
+        <f>F7*F8</f>
         <v>31.500000000000004</v>
       </c>
       <c r="G6" s="83">
-        <f t="shared" si="1"/>
+        <f>G7*G8</f>
         <v>39.847500000000004</v>
       </c>
       <c r="H6" s="83">
-        <f t="shared" si="1"/>
+        <f>H7*H8</f>
         <v>50.820000000000007</v>
       </c>
       <c r="I6" s="83">
-        <f t="shared" si="1"/>
+        <f>I7*I8</f>
         <v>64.287300000000016</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D7" s="29"/>
       <c r="E7" s="83">
@@ -1794,13 +1838,13 @@
         <v>920</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="E8" s="83">
         <f>'lộ trình hp'!B8</f>
@@ -1823,12 +1867,12 @@
         <v>6.9877500000000023E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>2</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="29"/>
@@ -1837,29 +1881,29 @@
         <v>34.450000000000003</v>
       </c>
       <c r="F9" s="87">
-        <f t="shared" ref="F9:I9" si="2">F11*F10</f>
+        <f>F11*F10</f>
         <v>36.172499999999999</v>
       </c>
       <c r="G9" s="87">
-        <f t="shared" si="2"/>
+        <f>G11*G10</f>
         <v>57.049199999999999</v>
       </c>
       <c r="H9" s="87">
-        <f t="shared" si="2"/>
+        <f>H11*H10</f>
         <v>66.144000000000005</v>
       </c>
       <c r="I9" s="87">
-        <f t="shared" si="2"/>
+        <f>I11*I10</f>
         <v>76.065600000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D10" s="29"/>
       <c r="E10" s="83">
@@ -1883,13 +1927,13 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="83">
@@ -1897,28 +1941,28 @@
         <v>6.8900000000000003E-2</v>
       </c>
       <c r="F11" s="83">
-        <f t="shared" ref="F11:I11" si="3">0.13*53%</f>
+        <f>0.13*53%</f>
         <v>6.8900000000000003E-2</v>
       </c>
       <c r="G11" s="83">
-        <f t="shared" si="3"/>
+        <f>0.13*53%</f>
         <v>6.8900000000000003E-2</v>
       </c>
       <c r="H11" s="83">
-        <f t="shared" si="3"/>
+        <f>0.13*53%</f>
         <v>6.8900000000000003E-2</v>
       </c>
       <c r="I11" s="83">
-        <f t="shared" si="3"/>
+        <f>0.13*53%</f>
         <v>6.8900000000000003E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="8"/>
@@ -1927,28 +1971,28 @@
         <v>39.753000000000007</v>
       </c>
       <c r="F12" s="88">
-        <f t="shared" ref="F12:I12" si="4">F13+F16+F17+F18+F19+F20+F21+F22+F24+F25</f>
+        <f>F13+F16+F17+F18+F19+F20+F21+F22+F24+F25</f>
         <v>55.107150000000019</v>
       </c>
       <c r="G12" s="88">
-        <f t="shared" si="4"/>
+        <f>G13+G16+G17+G18+G19+G20+G21+G22+G24+G25</f>
         <v>80.324073000000013</v>
       </c>
       <c r="H12" s="88">
-        <f t="shared" si="4"/>
+        <f>H13+H16+H17+H18+H19+H20+H21+H22+H24+H25</f>
         <v>96.224760000000003</v>
       </c>
       <c r="I12" s="88">
-        <f t="shared" si="4"/>
+        <f>I13+I16+I17+I18+I19+I20+I21+I22+I24+I25</f>
         <v>114.57415500000003</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="11"/>
@@ -1957,29 +2001,29 @@
         <v>4.7650000000000006</v>
       </c>
       <c r="F13" s="89">
-        <f t="shared" ref="F13:I13" si="5">F14+F15</f>
+        <f>F14+F15</f>
         <v>7.3972500000000005</v>
       </c>
       <c r="G13" s="89">
-        <f t="shared" si="5"/>
+        <f>G14+G15</f>
         <v>10.48662</v>
       </c>
       <c r="H13" s="89">
-        <f t="shared" si="5"/>
+        <f>H14+H15</f>
         <v>12.712800000000001</v>
       </c>
       <c r="I13" s="89">
-        <f t="shared" si="5"/>
+        <f>I14+I15</f>
         <v>15.321036000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A14" s="107"/>
+    <row r="14" spans="1:9" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="126"/>
       <c r="B14" s="12" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D14" s="14">
         <v>0.12</v>
@@ -2005,13 +2049,13 @@
         <v>7.7144760000000012</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="108"/>
+    <row r="15" spans="1:9" s="15" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="127"/>
       <c r="B15" s="12" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D15" s="16">
         <v>0.1</v>
@@ -2037,15 +2081,15 @@
         <v>7.6065600000000009</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>2</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D16" s="16">
         <v>0.1</v>
@@ -2071,15 +2115,15 @@
         <v>7.6065600000000009</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>3</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D17" s="16">
         <v>0.1</v>
@@ -2105,15 +2149,15 @@
         <v>7.6065600000000009</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>4</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D18" s="18">
         <v>0.2</v>
@@ -2139,15 +2183,15 @@
         <v>28.070580000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>5</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D19" s="18">
         <v>0.05</v>
@@ -2173,15 +2217,15 @@
         <v>7.0176450000000017</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>6</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D20" s="18">
         <v>0.04</v>
@@ -2207,15 +2251,15 @@
         <v>3.042624</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D21" s="18">
         <v>0.05</v>
@@ -2241,15 +2285,15 @@
         <v>3.8032800000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D22" s="18">
         <v>0.1</v>
@@ -2259,31 +2303,31 @@
         <v>4.5450000000000008</v>
       </c>
       <c r="F22" s="91">
-        <f t="shared" ref="F22:I22" si="6">F5*$D$22</f>
+        <f>F5*$D$22</f>
         <v>6.7672500000000007</v>
       </c>
       <c r="G22" s="91">
-        <f t="shared" si="6"/>
+        <f>G5*$D$22</f>
         <v>9.6896700000000013</v>
       </c>
       <c r="H22" s="91">
-        <f t="shared" si="6"/>
+        <f>H5*$D$22</f>
         <v>11.696400000000002</v>
       </c>
       <c r="I22" s="91">
-        <f t="shared" si="6"/>
+        <f>I5*$D$22</f>
         <v>14.035290000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D23" s="18">
         <v>0.1</v>
@@ -2293,31 +2337,31 @@
         <v>0.45450000000000013</v>
       </c>
       <c r="F23" s="91">
-        <f>F6*D23</f>
-        <v>3.1500000000000004</v>
+        <f>F22*$D23</f>
+        <v>0.67672500000000013</v>
       </c>
       <c r="G23" s="91">
-        <f>G6*D23</f>
-        <v>3.9847500000000005</v>
+        <f>G22*$D23</f>
+        <v>0.96896700000000013</v>
       </c>
       <c r="H23" s="91">
-        <f>H6*D23</f>
-        <v>5.0820000000000007</v>
+        <f>H22*$D23</f>
+        <v>1.1696400000000002</v>
       </c>
       <c r="I23" s="91">
-        <f>I6*D23</f>
-        <v>6.4287300000000016</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+        <f>I22*$D23</f>
+        <v>1.4035290000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D24" s="18">
         <v>0.1</v>
@@ -2343,15 +2387,15 @@
         <v>14.035290000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <v>11</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D25" s="18">
         <v>0.1</v>
@@ -2377,12 +2421,12 @@
         <v>14.035290000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="30" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" s="30" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="40" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="8">
@@ -2394,47 +2438,47 @@
         <v>5.6969999999999956</v>
       </c>
       <c r="F26" s="92">
-        <f t="shared" ref="F26:I26" si="7">F5-F12</f>
+        <f>F5-F12</f>
         <v>12.565349999999981</v>
       </c>
       <c r="G26" s="92">
-        <f t="shared" si="7"/>
+        <f>G5-G12</f>
         <v>16.572626999999997</v>
       </c>
       <c r="H26" s="92">
-        <f t="shared" si="7"/>
+        <f>H5-H12</f>
         <v>20.739240000000009</v>
       </c>
       <c r="I26" s="92">
-        <f t="shared" si="7"/>
+        <f>I5-I12</f>
         <v>25.778745000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
       <c r="B27" s="21"/>
       <c r="C27" s="22"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="109" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="109"/>
-    </row>
-    <row r="28" spans="1:9" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="E27" s="124" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="122"/>
+    </row>
+    <row r="28" spans="1:9" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22"/>
       <c r="B28" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="104" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="104"/>
-      <c r="E28" s="110" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="110"/>
-    </row>
-    <row r="29" spans="1:9" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="C28" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="122"/>
+      <c r="E28" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" s="122"/>
+    </row>
+    <row r="29" spans="1:9" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -2442,7 +2486,7 @@
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
     </row>
-    <row r="30" spans="1:9" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -2450,7 +2494,7 @@
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
     </row>
-    <row r="31" spans="1:9" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20"/>
       <c r="B31" s="21"/>
       <c r="C31" s="21"/>
@@ -2458,7 +2502,7 @@
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
     </row>
-    <row r="32" spans="1:9" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20"/>
       <c r="B32" s="21"/>
       <c r="C32" s="21"/>
@@ -2466,115 +2510,114 @@
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
     </row>
-    <row r="33" spans="1:6" s="23" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" s="23" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20"/>
       <c r="B33" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="104" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="104"/>
-      <c r="E33" s="105" t="s">
-        <v>35</v>
-      </c>
-      <c r="F33" s="105"/>
+        <v>45</v>
+      </c>
+      <c r="C33" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="122"/>
+      <c r="E33" s="123" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="A14:A15"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="23.44140625" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="118" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+    </row>
+    <row r="4" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-    </row>
-    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-    </row>
-    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="93">
@@ -2598,12 +2641,12 @@
         <v>2627.9245125000007</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="8"/>
@@ -2613,98 +2656,98 @@
       </c>
       <c r="F6" s="84">
         <f>SUM(F7:F18)</f>
-        <v>1354.2549999999999</v>
+        <v>1241.7369999999999</v>
       </c>
       <c r="G6" s="84">
         <f>SUM(G7:G18)</f>
-        <v>1633.8104125000004</v>
+        <v>1497.9449275000004</v>
       </c>
       <c r="H6" s="84">
         <f>SUM(H7:H18)</f>
-        <v>1987.4648500000005</v>
+        <v>1822.0633900000005</v>
       </c>
       <c r="I6" s="84">
         <f>SUM(I7:I18)</f>
-        <v>2398.4113063750005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+        <v>2198.6890434250004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>1</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D7" s="18">
         <v>0.1</v>
       </c>
       <c r="E7" s="85">
-        <f>E$5*D7</f>
+        <f t="shared" ref="E7:E14" si="0">E$5*D7</f>
         <v>51.7</v>
       </c>
       <c r="F7" s="85">
-        <f>F$5*D7</f>
+        <f t="shared" ref="F7:F14" si="1">F$5*D7</f>
         <v>148.05000000000004</v>
       </c>
       <c r="G7" s="85">
-        <f>G$5*D7</f>
+        <f t="shared" ref="G7:G14" si="2">G$5*D7</f>
         <v>178.77037500000006</v>
       </c>
       <c r="H7" s="85">
-        <f>H$5*D7</f>
+        <f t="shared" ref="H7:H14" si="3">H$5*D7</f>
         <v>217.63350000000005</v>
       </c>
       <c r="I7" s="85">
-        <f>I$5*D7</f>
+        <f t="shared" ref="I7:I14" si="4">I$5*D7</f>
         <v>262.79245125000006</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>2</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D8" s="18">
         <v>0.01</v>
       </c>
       <c r="E8" s="85">
-        <f t="shared" ref="E8:E18" si="0">E$5*D8</f>
+        <f t="shared" si="0"/>
         <v>5.17</v>
       </c>
       <c r="F8" s="85">
-        <f t="shared" ref="F8:F18" si="1">F$5*D8</f>
+        <f t="shared" si="1"/>
         <v>14.805000000000003</v>
       </c>
       <c r="G8" s="85">
-        <f t="shared" ref="G8:G18" si="2">G$5*D8</f>
+        <f t="shared" si="2"/>
         <v>17.877037500000004</v>
       </c>
       <c r="H8" s="85">
-        <f t="shared" ref="H8:H18" si="3">H$5*D8</f>
+        <f t="shared" si="3"/>
         <v>21.763350000000006</v>
       </c>
       <c r="I8" s="85">
-        <f t="shared" ref="I8:I18" si="4">I$5*D8</f>
+        <f t="shared" si="4"/>
         <v>26.279245125000006</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>3</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D9" s="18">
         <v>0.01</v>
@@ -2731,15 +2774,15 @@
       </c>
       <c r="K9" s="42"/>
     </row>
-    <row r="10" spans="1:11" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>4</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D10" s="18">
         <v>0.12</v>
@@ -2749,7 +2792,7 @@
         <v>62.04</v>
       </c>
       <c r="F10" s="85">
-        <f>F$5*D10</f>
+        <f t="shared" si="1"/>
         <v>177.66000000000003</v>
       </c>
       <c r="G10" s="85">
@@ -2766,15 +2809,15 @@
       </c>
       <c r="K10" s="42"/>
     </row>
-    <row r="11" spans="1:11" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>5</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D11" s="18">
         <v>0.12</v>
@@ -2801,15 +2844,15 @@
       </c>
       <c r="K11" s="42"/>
     </row>
-    <row r="12" spans="1:11" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>6</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D12" s="18">
         <v>0.25</v>
@@ -2836,15 +2879,15 @@
       </c>
       <c r="K12" s="42"/>
     </row>
-    <row r="13" spans="1:11" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>7</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D13" s="18">
         <v>7.0000000000000007E-2</v>
@@ -2871,15 +2914,15 @@
       </c>
       <c r="K13" s="42"/>
     </row>
-    <row r="14" spans="1:11" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>8</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D14" s="18">
         <v>0.01</v>
@@ -2906,15 +2949,15 @@
       </c>
       <c r="K14" s="43"/>
     </row>
-    <row r="15" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>9</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D15" s="18">
         <v>0.1</v>
@@ -2924,70 +2967,70 @@
         <v>12.408000000000001</v>
       </c>
       <c r="F15" s="85">
-        <f t="shared" si="1"/>
-        <v>148.05000000000004</v>
+        <f>(F10+F11)*$D15</f>
+        <v>35.532000000000004</v>
       </c>
       <c r="G15" s="85">
-        <f t="shared" si="2"/>
-        <v>178.77037500000006</v>
+        <f>(G10+G11)*$D15</f>
+        <v>42.904890000000009</v>
       </c>
       <c r="H15" s="85">
-        <f t="shared" si="3"/>
-        <v>217.63350000000005</v>
+        <f>(H10+H11)*$D15</f>
+        <v>52.232040000000012</v>
       </c>
       <c r="I15" s="85">
-        <f t="shared" si="4"/>
-        <v>262.79245125000006</v>
+        <f>(I10+I11)*$D15</f>
+        <v>63.070188300000019</v>
       </c>
       <c r="K15" s="44"/>
     </row>
-    <row r="16" spans="1:11" ht="33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>10</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D16" s="18">
         <v>0.1</v>
       </c>
       <c r="E16" s="85">
-        <f t="shared" si="0"/>
+        <f>E$5*D16</f>
         <v>51.7</v>
       </c>
       <c r="F16" s="85">
-        <f t="shared" si="1"/>
+        <f>F$5*D16</f>
         <v>148.05000000000004</v>
       </c>
       <c r="G16" s="85">
-        <f t="shared" si="2"/>
+        <f>G$5*D16</f>
         <v>178.77037500000006</v>
       </c>
       <c r="H16" s="85">
-        <f t="shared" si="3"/>
+        <f>H$5*D16</f>
         <v>217.63350000000005</v>
       </c>
       <c r="I16" s="85">
-        <f t="shared" si="4"/>
+        <f>I$5*D16</f>
         <v>262.79245125000006</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>11</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="18">
         <v>0.08</v>
       </c>
       <c r="E17" s="85" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="F17" s="85">
         <v>7</v>
@@ -3002,49 +3045,49 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>12</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D18" s="18">
         <v>0.02</v>
       </c>
       <c r="E18" s="85">
-        <f t="shared" si="0"/>
+        <f>E$5*D18</f>
         <v>10.34</v>
       </c>
       <c r="F18" s="85">
-        <f t="shared" si="1"/>
+        <f>F$5*D18</f>
         <v>29.610000000000007</v>
       </c>
       <c r="G18" s="85">
-        <f t="shared" si="2"/>
+        <f>G$5*D18</f>
         <v>35.754075000000007</v>
       </c>
       <c r="H18" s="85">
-        <f t="shared" si="3"/>
+        <f>H$5*D18</f>
         <v>43.526700000000012</v>
       </c>
       <c r="I18" s="85">
-        <f t="shared" si="4"/>
+        <f>I$5*D18</f>
         <v>52.558490250000013</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="30" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="30" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="40" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B19" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="84">
@@ -3053,177 +3096,176 @@
       </c>
       <c r="F19" s="84">
         <f>F5-F6</f>
-        <v>126.24500000000035</v>
+        <v>238.76300000000037</v>
       </c>
       <c r="G19" s="84">
         <f>G5-G6</f>
-        <v>153.89333749999992</v>
+        <v>289.75882249999995</v>
       </c>
       <c r="H19" s="84">
         <f>H5-H6</f>
-        <v>188.87014999999997</v>
+        <v>354.27161000000001</v>
       </c>
       <c r="I19" s="84">
         <f>I5-I6</f>
-        <v>229.51320612500012</v>
+        <v>429.23546907500031</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q29"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Q30"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+    </row>
+    <row r="2" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="118" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+    </row>
+    <row r="3" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F3" s="128" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="129"/>
+      <c r="H3" s="76"/>
+    </row>
+    <row r="4" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-    </row>
-    <row r="2" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-    </row>
-    <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="F3" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="111"/>
-      <c r="H3" s="76"/>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H4">
+        <v>54</v>
+      </c>
+      <c r="H4" s="109">
         <v>1000000</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C5" s="93">
         <f>SUM(C6:C8)</f>
         <v>562.45000000000005</v>
       </c>
       <c r="D5" s="93">
-        <f t="shared" ref="D5:G5" si="0">SUM(D6:D8)</f>
+        <f>SUM(D6:D8)</f>
         <v>1548.1725000000001</v>
       </c>
       <c r="E5" s="93">
+        <f>SUM(E6:E8)</f>
+        <v>1884.6004500000004</v>
+      </c>
+      <c r="F5" s="93">
+        <f>SUM(F6:F8)</f>
+        <v>2293.2990000000009</v>
+      </c>
+      <c r="G5" s="93">
+        <f>SUM(G6:G8)</f>
+        <v>2768.2774125000005</v>
+      </c>
+      <c r="H5" s="110">
+        <f t="shared" ref="H5:Q5" si="0">C5/$H4</f>
+        <v>5.6245000000000004E-4</v>
+      </c>
+      <c r="I5" s="110">
         <f t="shared" si="0"/>
-        <v>1884.6004500000004</v>
-      </c>
-      <c r="F5" s="93">
+        <v>1.5481725000000002E-3</v>
+      </c>
+      <c r="J5" s="110">
         <f t="shared" si="0"/>
-        <v>2293.2990000000009</v>
-      </c>
-      <c r="G5" s="93">
+        <v>1.8846004500000003E-3</v>
+      </c>
+      <c r="K5" s="110">
         <f t="shared" si="0"/>
-        <v>2768.2774125000005</v>
-      </c>
-      <c r="H5" s="80">
-        <f>C5/$H4</f>
-        <v>5.6245000000000004E-4</v>
-      </c>
-      <c r="I5" s="80">
-        <f t="shared" ref="I5:Q5" si="1">D5/$H4</f>
-        <v>1.5481725000000002E-3</v>
-      </c>
-      <c r="J5" s="80">
-        <f t="shared" si="1"/>
-        <v>1.8846004500000003E-3</v>
-      </c>
-      <c r="K5" s="80">
-        <f t="shared" si="1"/>
         <v>2.2932990000000008E-3</v>
       </c>
-      <c r="L5" s="80">
-        <f>G5/$H4</f>
+      <c r="L5" s="110">
+        <f t="shared" si="0"/>
         <v>2.7682774125000007E-3</v>
       </c>
-      <c r="M5" s="80">
-        <f t="shared" si="1"/>
+      <c r="M5" s="110">
+        <f t="shared" si="0"/>
         <v>5.6245000000000006E-10</v>
       </c>
-      <c r="N5" s="80">
-        <f t="shared" si="1"/>
+      <c r="N5" s="110">
+        <f t="shared" si="0"/>
         <v>1.5481725000000002E-9</v>
       </c>
-      <c r="O5" s="80">
-        <f t="shared" si="1"/>
+      <c r="O5" s="110">
+        <f t="shared" si="0"/>
         <v>1.8846004500000004E-9</v>
       </c>
-      <c r="P5" s="80">
-        <f t="shared" si="1"/>
+      <c r="P5" s="110">
+        <f t="shared" si="0"/>
         <v>2.2932990000000009E-9</v>
       </c>
-      <c r="Q5" s="80">
-        <f t="shared" si="1"/>
+      <c r="Q5" s="110">
+        <f t="shared" si="0"/>
         <v>2.7682774125000009E-9</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C6" s="94">
         <f>'Nội dung khoán tHU CHI học phí'!E5</f>
@@ -3245,33 +3287,33 @@
         <f>'Nội dung khoán tHU CHI học phí'!I5</f>
         <v>2627.9245125000007</v>
       </c>
-      <c r="H6" s="80">
-        <f>C6/$H$4</f>
+      <c r="H6" s="110">
+        <f t="shared" ref="H6:L8" si="1">C6/$H$4</f>
         <v>5.1699999999999999E-4</v>
       </c>
-      <c r="I6" s="80">
-        <f t="shared" ref="I6:L8" si="2">D6/$H$4</f>
+      <c r="I6" s="110">
+        <f t="shared" si="1"/>
         <v>1.4805000000000003E-3</v>
       </c>
-      <c r="J6" s="80">
-        <f t="shared" si="2"/>
+      <c r="J6" s="110">
+        <f t="shared" si="1"/>
         <v>1.7877037500000003E-3</v>
       </c>
-      <c r="K6" s="80">
-        <f t="shared" si="2"/>
+      <c r="K6" s="110">
+        <f t="shared" si="1"/>
         <v>2.1763350000000006E-3</v>
       </c>
-      <c r="L6" s="80">
-        <f t="shared" si="2"/>
+      <c r="L6" s="110">
+        <f t="shared" si="1"/>
         <v>2.6279245125000006E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="C7" s="94">
         <f>'Nội dung khoán THU CHI thuê sân'!E6</f>
@@ -3293,33 +3335,33 @@
         <f>'Nội dung khoán THU CHI thuê sân'!I6</f>
         <v>64.287300000000016</v>
       </c>
-      <c r="H7" s="80">
-        <f>C7/$H$4</f>
+      <c r="H7" s="110">
+        <f t="shared" si="1"/>
         <v>1.1E-5</v>
       </c>
-      <c r="I7" s="80">
-        <f t="shared" si="2"/>
+      <c r="I7" s="110">
+        <f t="shared" si="1"/>
         <v>3.1500000000000007E-5</v>
       </c>
-      <c r="J7" s="80">
-        <f t="shared" si="2"/>
+      <c r="J7" s="110">
+        <f t="shared" si="1"/>
         <v>3.9847500000000001E-5</v>
       </c>
-      <c r="K7" s="80">
-        <f t="shared" si="2"/>
+      <c r="K7" s="110">
+        <f t="shared" si="1"/>
         <v>5.0820000000000005E-5</v>
       </c>
-      <c r="L7" s="80">
-        <f t="shared" si="2"/>
+      <c r="L7" s="110">
+        <f t="shared" si="1"/>
         <v>6.428730000000001E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="C8" s="94">
         <f>'Nội dung khoán THU CHI thuê sân'!E9</f>
@@ -3341,62 +3383,62 @@
         <f>'Nội dung khoán THU CHI thuê sân'!I9</f>
         <v>76.065600000000003</v>
       </c>
-      <c r="H8" s="80">
-        <f>C8/$H$4</f>
+      <c r="H8" s="110">
+        <f t="shared" si="1"/>
         <v>3.4450000000000004E-5</v>
       </c>
-      <c r="I8" s="80">
-        <f t="shared" si="2"/>
+      <c r="I8" s="110">
+        <f t="shared" si="1"/>
         <v>3.61725E-5</v>
       </c>
-      <c r="J8" s="80">
-        <f t="shared" si="2"/>
+      <c r="J8" s="110">
+        <f t="shared" si="1"/>
         <v>5.7049199999999996E-5</v>
       </c>
-      <c r="K8" s="80">
-        <f t="shared" si="2"/>
+      <c r="K8" s="110">
+        <f t="shared" si="1"/>
         <v>6.6144000000000009E-5</v>
       </c>
-      <c r="L8" s="80">
-        <f t="shared" si="2"/>
+      <c r="L8" s="110">
+        <f t="shared" si="1"/>
         <v>7.6065599999999999E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C9" s="84">
         <f>SUM(C10:C21)</f>
         <v>616.04853880000007</v>
       </c>
       <c r="D9" s="84">
-        <f t="shared" ref="D9:G9" si="3">SUM(D10:D21)</f>
+        <f>SUM(D10:D21)</f>
         <v>1413.4057513000002</v>
       </c>
       <c r="E9" s="84">
-        <f t="shared" si="3"/>
+        <f>SUM(E10:E21)</f>
         <v>1674.5838943000001</v>
       </c>
       <c r="F9" s="84">
-        <f t="shared" si="3"/>
+        <f>SUM(F10:F21)</f>
         <v>1998.8121088000005</v>
       </c>
       <c r="G9" s="84">
-        <f t="shared" si="3"/>
+        <f>SUM(G10:G21)</f>
         <v>2375.5767535000005</v>
       </c>
       <c r="H9" s="80"/>
     </row>
-    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>1</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C10" s="85">
         <f>'Nội dung khoán tHU CHI học phí'!E7+'Nội dung khoán THU CHI thuê sân'!E14+'Nội dung khoán THU CHI thuê sân'!E15</f>
@@ -3419,12 +3461,12 @@
         <v>278.11348725000005</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>2</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="C11" s="85">
         <f>'Khấu hao'!$I$17-'Khấu hao'!I13-'Khấu hao'!I15</f>
@@ -3447,12 +3489,12 @@
         <v>174.24728879999998</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>4</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C12" s="85">
         <f>'Nội dung khoán tHU CHI học phí'!E10</f>
@@ -3476,12 +3518,12 @@
       </c>
       <c r="I12" s="42"/>
     </row>
-    <row r="13" spans="1:17" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>5</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C13" s="85">
         <f>'Nội dung khoán tHU CHI học phí'!E11</f>
@@ -3505,12 +3547,12 @@
       </c>
       <c r="I13" s="42"/>
     </row>
-    <row r="14" spans="1:17" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>6</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="C14" s="85">
         <f>'Nội dung khoán THU CHI thuê sân'!E22</f>
@@ -3534,12 +3576,12 @@
       </c>
       <c r="I14" s="42"/>
     </row>
-    <row r="15" spans="1:17" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>6</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C15" s="85">
         <f>'Nội dung khoán tHU CHI học phí'!E12</f>
@@ -3563,41 +3605,41 @@
       </c>
       <c r="I15" s="42"/>
     </row>
-    <row r="16" spans="1:17" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>7</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C16" s="85">
         <f>C6*0.07</f>
         <v>36.190000000000005</v>
       </c>
       <c r="D16" s="85">
-        <f t="shared" ref="D16:G16" si="4">D6*0.07</f>
+        <f>D6*0.07</f>
         <v>103.63500000000002</v>
       </c>
       <c r="E16" s="85">
-        <f t="shared" si="4"/>
+        <f>E6*0.07</f>
         <v>125.13926250000004</v>
       </c>
       <c r="F16" s="85">
-        <f t="shared" si="4"/>
+        <f>F6*0.07</f>
         <v>152.34345000000005</v>
       </c>
       <c r="G16" s="85">
-        <f t="shared" si="4"/>
+        <f>G6*0.07</f>
         <v>183.95471587500006</v>
       </c>
       <c r="I16" s="42"/>
     </row>
-    <row r="17" spans="1:9" s="15" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="15" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>8</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="C17" s="85">
         <f>'Nội dung khoán THU CHI thuê sân'!E20+'Nội dung khoán tHU CHI học phí'!E14</f>
@@ -3621,69 +3663,69 @@
       </c>
       <c r="I17" s="43"/>
     </row>
-    <row r="18" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>9</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C18" s="85">
         <f>(C12+C13+C14)*0.15</f>
         <v>19.293749999999999</v>
       </c>
       <c r="D18" s="85">
-        <f t="shared" ref="D18:G18" si="5">(D12+D13+D14)*0.15</f>
+        <f>(D12+D13+D14)*0.15</f>
         <v>54.313087500000002</v>
       </c>
       <c r="E18" s="85">
-        <f t="shared" si="5"/>
+        <f>(E12+E13+E14)*0.15</f>
         <v>65.810785500000009</v>
       </c>
       <c r="F18" s="85">
-        <f t="shared" si="5"/>
+        <f>(F12+F13+F14)*0.15</f>
         <v>80.102520000000013</v>
       </c>
       <c r="G18" s="85">
-        <f t="shared" si="5"/>
+        <f>(G12+G13+G14)*0.15</f>
         <v>96.710575950000035</v>
       </c>
       <c r="I18" s="44"/>
     </row>
-    <row r="19" spans="1:9" ht="33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>10</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="C19" s="85">
         <f>C5*0.1</f>
         <v>56.245000000000005</v>
       </c>
       <c r="D19" s="85">
-        <f t="shared" ref="D19:G19" si="6">D5*0.1</f>
+        <f>D5*0.1</f>
         <v>154.81725000000003</v>
       </c>
       <c r="E19" s="85">
-        <f t="shared" si="6"/>
+        <f>E5*0.1</f>
         <v>188.46004500000004</v>
       </c>
       <c r="F19" s="85">
-        <f t="shared" si="6"/>
+        <f>F5*0.1</f>
         <v>229.32990000000009</v>
       </c>
       <c r="G19" s="85">
-        <f t="shared" si="6"/>
+        <f>G5*0.1</f>
         <v>276.82774125000009</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>11</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="C20" s="85">
         <v>61.2</v>
@@ -3701,120 +3743,120 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>12</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C21" s="85">
         <f>C5*1%</f>
         <v>5.6245000000000003</v>
       </c>
       <c r="D21" s="85">
-        <f t="shared" ref="D21:G21" si="7">D5*1%</f>
+        <f>D5*1%</f>
         <v>15.481725000000001</v>
       </c>
       <c r="E21" s="85">
-        <f t="shared" si="7"/>
+        <f>E5*1%</f>
         <v>18.846004500000003</v>
       </c>
       <c r="F21" s="85">
-        <f t="shared" si="7"/>
+        <f>F5*1%</f>
         <v>22.932990000000011</v>
       </c>
       <c r="G21" s="85">
-        <f t="shared" si="7"/>
+        <f>G5*1%</f>
         <v>27.682774125000005</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="30" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" s="30" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="40" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C22" s="84">
         <f>C5-C9</f>
         <v>-53.598538800000028</v>
       </c>
       <c r="D22" s="84">
-        <f t="shared" ref="D22:G22" si="8">D5-D9</f>
+        <f>D5-D9</f>
         <v>134.76674869999988</v>
       </c>
       <c r="E22" s="84">
-        <f t="shared" si="8"/>
+        <f>E5-E9</f>
         <v>210.01655570000025</v>
       </c>
       <c r="F22" s="84">
-        <f t="shared" si="8"/>
+        <f>F5-F9</f>
         <v>294.4868912000004</v>
       </c>
       <c r="G22" s="84">
-        <f t="shared" si="8"/>
+        <f>G5-G9</f>
         <v>392.70065900000009</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="68"/>
       <c r="B23" s="71" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C23" s="95">
         <f>(C7+C8)*5%</f>
         <v>2.2725000000000004</v>
       </c>
       <c r="D23" s="95">
-        <f t="shared" ref="D23:G23" si="9">(D7+D8)*5%</f>
+        <f>(D7+D8)*5%</f>
         <v>3.3836250000000003</v>
       </c>
       <c r="E23" s="95">
-        <f t="shared" si="9"/>
+        <f>(E7+E8)*5%</f>
         <v>4.8448350000000007</v>
       </c>
       <c r="F23" s="95">
-        <f t="shared" si="9"/>
+        <f>(F7+F8)*5%</f>
         <v>5.8482000000000012</v>
       </c>
       <c r="G23" s="95">
-        <f t="shared" si="9"/>
+        <f>(G7+G8)*5%</f>
         <v>7.0176450000000017</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="68"/>
       <c r="B24" s="71" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C24" s="95">
         <f>(C8+C7)*5%+C6*2%</f>
         <v>12.612500000000001</v>
       </c>
       <c r="D24" s="95">
-        <f t="shared" ref="D24:G24" si="10">(D8+D7)*5%+D6*2%</f>
+        <f>(D8+D7)*5%+D6*2%</f>
         <v>32.993625000000009</v>
       </c>
       <c r="E24" s="95">
-        <f t="shared" si="10"/>
+        <f>(E8+E7)*5%+E6*2%</f>
         <v>40.598910000000011</v>
       </c>
       <c r="F24" s="95">
-        <f t="shared" si="10"/>
+        <f>(F8+F7)*5%+F6*2%</f>
         <v>49.374900000000011</v>
       </c>
       <c r="G24" s="95">
-        <f t="shared" si="10"/>
+        <f>(G8+G7)*5%+G6*2%</f>
         <v>59.576135250000014</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="69" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C25" s="96">
         <f>C22-C23-C24</f>
@@ -3825,24 +3867,24 @@
         <v>98.389498699999876</v>
       </c>
       <c r="E25" s="96">
-        <f t="shared" ref="D25:G25" si="11">E22-E23-E24</f>
+        <f>E22-E23-E24</f>
         <v>164.57281070000025</v>
       </c>
       <c r="F25" s="96">
-        <f t="shared" si="11"/>
+        <f>F22-F23-F24</f>
         <v>239.26379120000036</v>
       </c>
       <c r="G25" s="96">
-        <f t="shared" si="11"/>
+        <f>G22-G23-G24</f>
         <v>326.10687875000008</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="72" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B26" s="73" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C26" s="97"/>
       <c r="D26" s="97"/>
@@ -3850,12 +3892,12 @@
       <c r="F26" s="97"/>
       <c r="G26" s="97"/>
     </row>
-    <row r="27" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="75">
         <v>1</v>
       </c>
       <c r="B27" s="74" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C27" s="97">
         <f>'Khấu hao'!G17</f>
@@ -3866,106 +3908,134 @@
       <c r="F27" s="97"/>
       <c r="G27" s="97"/>
     </row>
-    <row r="28" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="75">
         <v>2</v>
       </c>
       <c r="B28" s="74" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C28" s="97">
         <f>C25+C11</f>
         <v>48.123749999999944</v>
       </c>
       <c r="D28" s="97">
-        <f t="shared" ref="D28:G28" si="12">D25+D11</f>
+        <f>D25+D11</f>
         <v>272.63678749999985</v>
       </c>
       <c r="E28" s="97">
-        <f t="shared" si="12"/>
+        <f>E25+E11</f>
         <v>338.8200995000002</v>
       </c>
       <c r="F28" s="97">
-        <f t="shared" si="12"/>
+        <f>F25+F11</f>
         <v>413.51108000000033</v>
       </c>
       <c r="G28" s="97">
-        <f t="shared" si="12"/>
+        <f>G25+G11</f>
         <v>500.35416755000006</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="75">
         <v>3</v>
       </c>
       <c r="B29" s="74" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C29" s="98">
-        <f>(C27-SUM(C28:G28))/(SUM(C28:G28)/4)+4</f>
-        <v>3.8264449124806728</v>
+        <f>IF(G30&lt;C27,"Chưa hoàn vốn trong 5 năm",IF(C30&gt;=C27,C27/C28,COUNTIF(C30:G30,"&lt;"&amp;C27)+(C27-INDEX(C30:G30,COUNTIF(C30:G30,"&lt;"&amp;C27)))/INDEX(C28:G28,COUNTIF(C30:G30,"&lt;"&amp;C27)+1)))</f>
+        <v>4.8635568783522167</v>
       </c>
       <c r="D29" s="97"/>
       <c r="E29" s="97"/>
       <c r="F29" s="97"/>
       <c r="G29" s="97"/>
     </row>
+    <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="A30" s="75" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="97">
+        <f>C28</f>
+        <v>48.123749999999944</v>
+      </c>
+      <c r="D30" s="97">
+        <f>C30+D28</f>
+        <v>320.76053749999983</v>
+      </c>
+      <c r="E30" s="97">
+        <f>D30+E28</f>
+        <v>659.58063700000002</v>
+      </c>
+      <c r="F30" s="97">
+        <f>E30+F28</f>
+        <v>1073.0917170000002</v>
+      </c>
+      <c r="G30" s="97">
+        <f>F30+G28</f>
+        <v>1573.4458845500003</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F3:G3"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" style="46" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="45" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="45" customWidth="1"/>
     <col min="4" max="4" width="8" style="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="45" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="45" customWidth="1"/>
-    <col min="7" max="8" width="12.5703125" style="45" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" style="45" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="45" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="45" customWidth="1"/>
+    <col min="7" max="8" width="12.5546875" style="45" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="45" customWidth="1"/>
     <col min="10" max="10" width="12" style="45" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="45"/>
+    <col min="11" max="11" width="9.109375" style="45" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="118" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
     </row>
     <row r="2" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-    </row>
-    <row r="3" spans="1:11" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="134" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="130"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+    </row>
+    <row r="3" spans="1:11" ht="24.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="60"/>
       <c r="B3" s="61"/>
       <c r="C3" s="60"/>
@@ -3975,82 +4045,82 @@
       <c r="G3" s="60"/>
       <c r="H3" s="60"/>
       <c r="I3" s="62" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="116" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="117">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="105" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="106">
         <v>1</v>
       </c>
-      <c r="B5" s="117">
+      <c r="B5" s="106">
         <v>2</v>
       </c>
-      <c r="C5" s="117">
+      <c r="C5" s="106">
         <v>3</v>
       </c>
-      <c r="D5" s="117">
+      <c r="D5" s="106">
         <v>4</v>
       </c>
-      <c r="E5" s="117">
+      <c r="E5" s="106">
         <v>5</v>
       </c>
-      <c r="F5" s="117">
+      <c r="F5" s="106">
         <v>6</v>
       </c>
-      <c r="G5" s="118" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="117">
+      <c r="G5" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="106">
         <v>8</v>
       </c>
-      <c r="I5" s="117" t="s">
-        <v>135</v>
-      </c>
-      <c r="J5" s="117">
+      <c r="I5" s="106" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="106">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="49" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" s="49" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="47">
         <v>1</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D6" s="47">
         <v>145</v>
@@ -4063,29 +4133,29 @@
         <v>0.1</v>
       </c>
       <c r="G6" s="63">
-        <f>E6*F6</f>
+        <f t="shared" ref="G6:G16" si="0">E6*F6</f>
         <v>61.43</v>
       </c>
       <c r="H6" s="78">
         <v>0.04</v>
       </c>
       <c r="I6" s="65">
-        <f>G6*H6</f>
+        <f t="shared" ref="I6:I16" si="1">G6*H6</f>
         <v>2.4571999999999998</v>
       </c>
       <c r="J6" s="47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="49" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="49" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47">
         <v>2</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D7" s="47">
         <v>70</v>
@@ -4098,29 +4168,29 @@
         <v>0.1</v>
       </c>
       <c r="G7" s="63">
-        <f t="shared" ref="G7:G16" si="0">E7*F7</f>
+        <f t="shared" si="0"/>
         <v>30.715</v>
       </c>
       <c r="H7" s="78">
         <v>0.04</v>
       </c>
       <c r="I7" s="65">
-        <f t="shared" ref="I7:I16" si="1">G7*H7</f>
+        <f t="shared" si="1"/>
         <v>1.2285999999999999</v>
       </c>
       <c r="J7" s="47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="49" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="49" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>3</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D8" s="47">
         <v>32</v>
@@ -4144,18 +4214,18 @@
         <v>6.7265888</v>
       </c>
       <c r="J8" s="47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="49" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="49" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47">
         <v>4</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D9" s="47">
         <v>1</v>
@@ -4178,18 +4248,18 @@
         <v>4.6689999999999996</v>
       </c>
       <c r="J9" s="47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="49" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="49" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47">
         <v>5</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D10" s="47">
         <v>2</v>
@@ -4213,18 +4283,18 @@
         <v>26</v>
       </c>
       <c r="J10" s="47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="49" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="49" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47">
         <v>6</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="D11" s="47">
         <v>3</v>
@@ -4248,18 +4318,18 @@
         <v>35.0259</v>
       </c>
       <c r="J11" s="47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="49" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="49" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47">
         <v>7</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D12" s="47">
         <v>1</v>
@@ -4282,22 +4352,22 @@
         <v>8</v>
       </c>
       <c r="J12" s="47" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="K12" s="49">
         <f>1/8</f>
         <v>0.125</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="49" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="49" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47">
         <v>8</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D13" s="47">
         <v>1</v>
@@ -4321,18 +4391,18 @@
         <v>29.5</v>
       </c>
       <c r="J13" s="47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="49" customFormat="1" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="49" customFormat="1" ht="173.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>9</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="D14" s="47">
         <v>1</v>
@@ -4355,18 +4425,18 @@
         <v>30</v>
       </c>
       <c r="J14" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="49" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="49" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47">
         <v>10</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="D15" s="47">
         <v>1</v>
@@ -4390,18 +4460,18 @@
         <v>28.14</v>
       </c>
       <c r="J15" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="49" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="49" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47">
         <v>11</v>
       </c>
       <c r="B16" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="47" t="s">
         <v>124</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>78</v>
       </c>
       <c r="D16" s="47">
         <v>1</v>
@@ -4425,21 +4495,21 @@
         <v>2.5</v>
       </c>
       <c r="J16" s="47" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="49" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="113" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="49" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="132" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
       <c r="E17" s="67">
         <f>SUM(E6:E16)</f>
         <v>3911.6880000000001</v>
       </c>
-      <c r="F17" s="115"/>
+      <c r="F17" s="104"/>
       <c r="G17" s="67">
         <f>SUM(G6:G16)</f>
         <v>1505.1760000000002</v>
@@ -4456,13 +4526,13 @@
       <c r="E18" s="53"/>
       <c r="F18" s="54"/>
     </row>
-    <row r="19" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="52"/>
       <c r="E19" s="53"/>
       <c r="G19" s="55"/>
       <c r="H19" s="55"/>
     </row>
-    <row r="20" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="56"/>
       <c r="E20" s="57"/>
       <c r="G20" s="58"/>
@@ -4481,46 +4551,46 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A3:F16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="C3" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="E3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="F3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="B4" s="35">
         <v>220</v>
@@ -4538,9 +4608,9 @@
         <v>920</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="B5" s="100">
         <f>'lộ trình hp'!B6</f>
@@ -4563,32 +4633,32 @@
         <v>2.8564396875000009</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="B6" s="101">
         <f>B4*B5</f>
         <v>517</v>
       </c>
       <c r="C6" s="101">
-        <f t="shared" ref="C6:F6" si="0">C4*C5</f>
+        <f>C4*C5</f>
         <v>1480.5000000000002</v>
       </c>
       <c r="D6" s="101">
-        <f t="shared" si="0"/>
+        <f>D4*D5</f>
         <v>1787.7037500000004</v>
       </c>
       <c r="E6" s="101">
-        <f t="shared" si="0"/>
+        <f>E4*E5</f>
         <v>2176.3350000000005</v>
       </c>
       <c r="F6" s="101">
-        <f t="shared" si="0"/>
+        <f>F4*F5</f>
         <v>2627.9245125000007</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="36"/>
       <c r="B7" s="36"/>
       <c r="C7" s="36"/>
@@ -4596,54 +4666,54 @@
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
     </row>
-    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="C8" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="E8" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="F8" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="B9" s="35">
         <f>B4</f>
         <v>220</v>
       </c>
       <c r="C9" s="35">
-        <f t="shared" ref="C9:F9" si="1">C4</f>
+        <f>C4</f>
         <v>600</v>
       </c>
       <c r="D9" s="35">
-        <f t="shared" si="1"/>
+        <f>D4</f>
         <v>690</v>
       </c>
       <c r="E9" s="35">
-        <f t="shared" si="1"/>
+        <f>E4</f>
         <v>800</v>
       </c>
       <c r="F9" s="35">
-        <f t="shared" si="1"/>
+        <f>F4</f>
         <v>920</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="B10" s="102">
         <f>'lộ trình hp'!B8</f>
@@ -4666,32 +4736,32 @@
         <v>6.9877500000000023E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B11" s="103">
         <f>B10*B9</f>
         <v>11</v>
       </c>
       <c r="C11" s="103">
-        <f t="shared" ref="C11:F11" si="2">C10*C9</f>
+        <f>C10*C9</f>
         <v>31.500000000000004</v>
       </c>
       <c r="D11" s="103">
-        <f t="shared" si="2"/>
+        <f>D10*D9</f>
         <v>39.847500000000004</v>
       </c>
       <c r="E11" s="103">
-        <f t="shared" si="2"/>
+        <f>E10*E9</f>
         <v>50.820000000000007</v>
       </c>
       <c r="F11" s="103">
-        <f t="shared" si="2"/>
+        <f>F10*F9</f>
         <v>64.287300000000016</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36"/>
       <c r="B12" s="36"/>
       <c r="C12" s="36"/>
@@ -4699,29 +4769,29 @@
       <c r="E12" s="36"/>
       <c r="F12" s="36"/>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="C13" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="E13" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="F13" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="B14" s="37">
         <v>500</v>
@@ -4743,52 +4813,664 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="119">
+        <v>135</v>
+      </c>
+      <c r="B15" s="108">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="C15" s="119">
+      <c r="C15" s="108">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="D15" s="119">
+      <c r="D15" s="108">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="E15" s="119">
+      <c r="E15" s="108">
         <v>6.8900000000000003E-2</v>
       </c>
-      <c r="F15" s="119">
+      <c r="F15" s="108">
         <v>6.8900000000000003E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B16" s="99">
         <f>B15*B14</f>
         <v>34.450000000000003</v>
       </c>
       <c r="C16" s="99">
-        <f t="shared" ref="C16" si="3">C15*C14</f>
+        <f>C15*C14</f>
         <v>36.172499999999999</v>
       </c>
       <c r="D16" s="99">
-        <f t="shared" ref="D16" si="4">D15*D14</f>
+        <f>D15*D14</f>
         <v>57.049199999999999</v>
       </c>
       <c r="E16" s="99">
-        <f t="shared" ref="E16" si="5">E15*E14</f>
+        <f>E15*E14</f>
         <v>66.144000000000005</v>
       </c>
       <c r="F16" s="99">
-        <f t="shared" ref="F16" si="6">F15*F14</f>
+        <f>F15*F14</f>
         <v>76.065600000000003</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="111" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="139" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+    </row>
+    <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="112" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="112" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="112" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="112" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="138" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="114">
+        <v>562.45000000000005</v>
+      </c>
+      <c r="D5" s="114">
+        <v>1548.17</v>
+      </c>
+      <c r="E5" s="114">
+        <v>1884.6</v>
+      </c>
+      <c r="F5" s="114">
+        <v>2293.3000000000002</v>
+      </c>
+      <c r="G5" s="114">
+        <v>2768.28</v>
+      </c>
+      <c r="H5" s="135">
+        <v>4.8600000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="136"/>
+      <c r="B6" s="113" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="114">
+        <v>616.04999999999995</v>
+      </c>
+      <c r="D6" s="114">
+        <v>1413.41</v>
+      </c>
+      <c r="E6" s="114">
+        <v>1674.58</v>
+      </c>
+      <c r="F6" s="114">
+        <v>1998.81</v>
+      </c>
+      <c r="G6" s="114">
+        <v>2375.58</v>
+      </c>
+      <c r="H6" s="136"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="136"/>
+      <c r="B7" s="113" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="114">
+        <v>-68.48</v>
+      </c>
+      <c r="D7" s="114">
+        <v>98.39</v>
+      </c>
+      <c r="E7" s="114">
+        <v>164.57</v>
+      </c>
+      <c r="F7" s="114">
+        <v>239.26</v>
+      </c>
+      <c r="G7" s="114">
+        <v>326.11</v>
+      </c>
+      <c r="H7" s="136"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="136"/>
+      <c r="B8" s="113" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="114">
+        <v>48.12</v>
+      </c>
+      <c r="D8" s="114">
+        <v>272.64</v>
+      </c>
+      <c r="E8" s="114">
+        <v>338.82</v>
+      </c>
+      <c r="F8" s="114">
+        <v>413.51</v>
+      </c>
+      <c r="G8" s="114">
+        <v>500.35</v>
+      </c>
+      <c r="H8" s="136"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="137"/>
+      <c r="B9" s="113" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="114">
+        <v>48.12</v>
+      </c>
+      <c r="D9" s="114">
+        <v>320.76</v>
+      </c>
+      <c r="E9" s="114">
+        <v>659.58</v>
+      </c>
+      <c r="F9" s="114">
+        <v>1073.0899999999999</v>
+      </c>
+      <c r="G9" s="114">
+        <v>1573.45</v>
+      </c>
+      <c r="H9" s="137"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="138" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="114">
+        <v>393.72</v>
+      </c>
+      <c r="D10" s="114">
+        <v>1083.72</v>
+      </c>
+      <c r="E10" s="114">
+        <v>1319.22</v>
+      </c>
+      <c r="F10" s="114">
+        <v>1605.31</v>
+      </c>
+      <c r="G10" s="114">
+        <v>1937.79</v>
+      </c>
+      <c r="H10" s="135" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="136"/>
+      <c r="B11" s="113" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="114">
+        <v>484.58</v>
+      </c>
+      <c r="D11" s="114">
+        <v>1043.76</v>
+      </c>
+      <c r="E11" s="114">
+        <v>1226.58</v>
+      </c>
+      <c r="F11" s="114">
+        <v>1453.54</v>
+      </c>
+      <c r="G11" s="114">
+        <v>1717.28</v>
+      </c>
+      <c r="H11" s="136"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="136"/>
+      <c r="B12" s="113" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="114">
+        <v>-101.28</v>
+      </c>
+      <c r="D12" s="114">
+        <v>14.5</v>
+      </c>
+      <c r="E12" s="114">
+        <v>60.83</v>
+      </c>
+      <c r="F12" s="114">
+        <v>113.11</v>
+      </c>
+      <c r="G12" s="114">
+        <v>173.9</v>
+      </c>
+      <c r="H12" s="136"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="136"/>
+      <c r="B13" s="113" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="114">
+        <v>15.33</v>
+      </c>
+      <c r="D13" s="114">
+        <v>188.75</v>
+      </c>
+      <c r="E13" s="114">
+        <v>235.07</v>
+      </c>
+      <c r="F13" s="114">
+        <v>287.36</v>
+      </c>
+      <c r="G13" s="114">
+        <v>348.15</v>
+      </c>
+      <c r="H13" s="136"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="137"/>
+      <c r="B14" s="113" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="114">
+        <v>15.33</v>
+      </c>
+      <c r="D14" s="114">
+        <v>204.07</v>
+      </c>
+      <c r="E14" s="114">
+        <v>439.15</v>
+      </c>
+      <c r="F14" s="114">
+        <v>726.5</v>
+      </c>
+      <c r="G14" s="114">
+        <v>1074.6500000000001</v>
+      </c>
+      <c r="H14" s="137"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="138" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="114">
+        <v>281.23</v>
+      </c>
+      <c r="D15" s="114">
+        <v>774.09</v>
+      </c>
+      <c r="E15" s="114">
+        <v>942.3</v>
+      </c>
+      <c r="F15" s="114">
+        <v>1146.6500000000001</v>
+      </c>
+      <c r="G15" s="114">
+        <v>1384.14</v>
+      </c>
+      <c r="H15" s="135" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="136"/>
+      <c r="B16" s="113" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="114">
+        <v>396.93</v>
+      </c>
+      <c r="D16" s="114">
+        <v>797.33</v>
+      </c>
+      <c r="E16" s="114">
+        <v>927.92</v>
+      </c>
+      <c r="F16" s="114">
+        <v>1090.03</v>
+      </c>
+      <c r="G16" s="114">
+        <v>1278.4100000000001</v>
+      </c>
+      <c r="H16" s="136"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="136"/>
+      <c r="B17" s="113" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="114">
+        <v>-123.15</v>
+      </c>
+      <c r="D17" s="114">
+        <v>-41.43</v>
+      </c>
+      <c r="E17" s="114">
+        <v>-8.34</v>
+      </c>
+      <c r="F17" s="114">
+        <v>29.01</v>
+      </c>
+      <c r="G17" s="114">
+        <v>72.430000000000007</v>
+      </c>
+      <c r="H17" s="136"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="136"/>
+      <c r="B18" s="113" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="114">
+        <v>-6.54</v>
+      </c>
+      <c r="D18" s="114">
+        <v>132.82</v>
+      </c>
+      <c r="E18" s="114">
+        <v>165.91</v>
+      </c>
+      <c r="F18" s="114">
+        <v>203.26</v>
+      </c>
+      <c r="G18" s="114">
+        <v>246.68</v>
+      </c>
+      <c r="H18" s="136"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="137"/>
+      <c r="B19" s="113" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="114">
+        <v>-6.54</v>
+      </c>
+      <c r="D19" s="114">
+        <v>126.28</v>
+      </c>
+      <c r="E19" s="114">
+        <v>292.19</v>
+      </c>
+      <c r="F19" s="114">
+        <v>495.45</v>
+      </c>
+      <c r="G19" s="114">
+        <v>742.12</v>
+      </c>
+      <c r="H19" s="137"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="115" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="H15:H19"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="H10:H14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="90" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="116" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="116" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1" s="116" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="116" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="117">
+        <v>1</v>
+      </c>
+      <c r="B2" s="117" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="117" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="117" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="117">
+        <v>2</v>
+      </c>
+      <c r="B3" s="117" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="117" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="117" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="117">
+        <v>3</v>
+      </c>
+      <c r="B4" s="117" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="117" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="117" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="117">
+        <v>4</v>
+      </c>
+      <c r="B5" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="117" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="117">
+        <v>5</v>
+      </c>
+      <c r="B6" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="117" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="117">
+        <v>6</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="117">
+        <v>7</v>
+      </c>
+      <c r="B8" s="117" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="117" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="117">
+        <v>8</v>
+      </c>
+      <c r="B9" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="117">
+        <v>9</v>
+      </c>
+      <c r="B10" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="117">
+        <v>10</v>
+      </c>
+      <c r="B11" s="117" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="117" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="117">
+        <v>11</v>
+      </c>
+      <c r="B12" s="117" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="117" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="117" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="117">
+        <v>12</v>
+      </c>
+      <c r="B13" s="117" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="117" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>